--- a/outputs/rankings/candidate_players_100.xlsx
+++ b/outputs/rankings/candidate_players_100.xlsx
@@ -516,7 +516,7 @@
         <v>2856</v>
       </c>
       <c r="H2" t="n">
-        <v>90.46927710843374</v>
+        <v>91.68915662650603</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -536,11 +536,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Florian Wirtz</t>
+          <t>Rayan Cherki</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -549,25 +549,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2351</v>
+        <v>2041</v>
       </c>
       <c r="H3" t="n">
-        <v>87.70384615384616</v>
+        <v>88.66153846153847</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>100000000</v>
+        <v>90000000</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -581,11 +581,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sávio</t>
+          <t>Bradley Barcola</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -594,29 +594,29 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Paris S-G</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1766</v>
+        <v>2181</v>
       </c>
       <c r="H4" t="n">
-        <v>86.82474182444062</v>
+        <v>87.69698795180723</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>200000</v>
+        <v>70000000</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>heuristic</t>
+          <t>transfermarkt</t>
         </is>
       </c>
     </row>
@@ -626,11 +626,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rayan Cherki</t>
+          <t>Florian Wirtz</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -639,25 +639,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2041</v>
+        <v>2351</v>
       </c>
       <c r="H5" t="n">
-        <v>86.46923076923078</v>
+        <v>87.35769230769232</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>90000000</v>
+        <v>100000000</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         <v>1730</v>
       </c>
       <c r="H6" t="n">
-        <v>85.98248709122204</v>
+        <v>86.93128227194494</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -716,11 +716,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bradley Barcola</t>
+          <t>Sávio</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -729,29 +729,29 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paris S-G</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2181</v>
+        <v>1766</v>
       </c>
       <c r="H7" t="n">
-        <v>85.82650602409639</v>
+        <v>85.48739242685025</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>70000000</v>
+        <v>200000</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>transfermarkt</t>
+          <t>heuristic</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>João Neves</t>
+          <t>Nicolás Paz</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -769,34 +769,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paris S-G</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1844</v>
+        <v>2687</v>
       </c>
       <c r="H8" t="n">
-        <v>84.29285714285716</v>
+        <v>84.10481927710845</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>140000000</v>
+        <v>400000</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>transfermarkt</t>
+          <t>heuristic</t>
         </is>
       </c>
     </row>
@@ -806,38 +806,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Matìas Soulé</t>
+          <t>João Neves</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Paris S-G</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1781</v>
+        <v>1844</v>
       </c>
       <c r="H9" t="n">
-        <v>83.0731712564544</v>
+        <v>83.82142857142857</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>35000000</v>
+        <v>140000000</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -851,11 +851,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nicolás Paz</t>
+          <t>Alejandro Garnacho</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -864,29 +864,29 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Manchester Utd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2687</v>
+        <v>2199</v>
       </c>
       <c r="H10" t="n">
-        <v>82.86686746987952</v>
+        <v>83.65963855421687</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>400000</v>
+        <v>28000000</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>heuristic</t>
+          <t>transfermarkt</t>
         </is>
       </c>
     </row>
@@ -896,20 +896,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jamie Gittens</t>
+          <t>Xavi Simons</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -918,16 +918,16 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1776</v>
+        <v>2150</v>
       </c>
       <c r="H11" t="n">
-        <v>82.7777108433735</v>
+        <v>83.34807692307693</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>30000000</v>
+        <v>40000000</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -941,38 +941,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alejandro Garnacho</t>
+          <t>Arda Güler</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Manchester Utd</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2199</v>
+        <v>1250</v>
       </c>
       <c r="H12" t="n">
-        <v>82.51204819277109</v>
+        <v>83.33406593406595</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>28000000</v>
+        <v>90000000</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>1750</v>
       </c>
       <c r="H13" t="n">
-        <v>82.0775817555938</v>
+        <v>83.11673838209983</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -1031,38 +1031,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pedri</t>
+          <t>Jamie Gittens</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2879</v>
+        <v>1776</v>
       </c>
       <c r="H14" t="n">
-        <v>81.61428571428573</v>
+        <v>83.09397590361446</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>150000000</v>
+        <v>30000000</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Xavi Simons</t>
+          <t>Jamal Musiala</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1098,16 +1098,16 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2150</v>
+        <v>1798</v>
       </c>
       <c r="H15" t="n">
-        <v>81.50192307692309</v>
+        <v>82.35247252747253</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>40000000</v>
+        <v>100000000</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tom Bischof</t>
+          <t>Pedri</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1134,25 +1134,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2559</v>
+        <v>2879</v>
       </c>
       <c r="H16" t="n">
-        <v>81.39285714285714</v>
+        <v>81.67857142857143</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>40000000</v>
+        <v>150000000</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Arda Güler</t>
+          <t>Tom Bischof</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1174,30 +1174,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1250</v>
+        <v>2559</v>
       </c>
       <c r="H17" t="n">
-        <v>81.19945054945057</v>
+        <v>81.56428571428572</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>90000000</v>
+        <v>40000000</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1211,38 +1211,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Warren Zaïre-Emery</t>
+          <t>Yankuba Minteh</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paris S-G</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2050</v>
+        <v>1838</v>
       </c>
       <c r="H18" t="n">
-        <v>81.07142857142858</v>
+        <v>81.54479345955249</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>80000000</v>
+        <v>45000000</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1256,38 +1256,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Yankuba Minteh</t>
+          <t>Warren Zaïre-Emery</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Paris S-G</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1838</v>
+        <v>2050</v>
       </c>
       <c r="H19" t="n">
-        <v>80.9393717728055</v>
+        <v>81.2</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>45000000</v>
+        <v>80000000</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jamal Musiala</t>
+          <t>Matìas Soulé</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1309,30 +1309,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1798</v>
+        <v>1781</v>
       </c>
       <c r="H20" t="n">
-        <v>80.73708791208792</v>
+        <v>80.90449655765921</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>100000000</v>
+        <v>35000000</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1346,11 +1346,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mohamed Ali Cho</t>
+          <t>Kenan Yıldız</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1621</v>
+        <v>2402</v>
       </c>
       <c r="H21" t="n">
-        <v>80.16060671256456</v>
+        <v>80.10180722891567</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>15000000</v>
+        <v>75000000</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1391,11 +1391,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kenan Yıldız</t>
+          <t>Dilane Bakwa</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1404,25 +1404,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2402</v>
+        <v>2497</v>
       </c>
       <c r="H22" t="n">
-        <v>79.94819277108435</v>
+        <v>79.73614457831326</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>75000000</v>
+        <v>28000000</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1436,11 +1436,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dilane Bakwa</t>
+          <t>Malick Fofana</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1458,16 +1458,16 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2497</v>
+        <v>1589</v>
       </c>
       <c r="H23" t="n">
-        <v>79.54638554216868</v>
+        <v>79.66086488812392</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>28000000</v>
+        <v>30000000</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>2341</v>
       </c>
       <c r="H24" t="n">
-        <v>79.3487951807229</v>
+        <v>79.43012048192772</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -1526,11 +1526,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Malick Fofana</t>
+          <t>Alberto Moleiro</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1539,25 +1539,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1589</v>
+        <v>2714</v>
       </c>
       <c r="H25" t="n">
-        <v>78.96508175559381</v>
+        <v>78.90301204819278</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>30000000</v>
+        <v>50000000</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Alberto Moleiro</t>
+          <t>Mohamed Ali Cho</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1584,25 +1584,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2714</v>
+        <v>1621</v>
       </c>
       <c r="H26" t="n">
-        <v>78.49638554216867</v>
+        <v>78.71482358003443</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>50000000</v>
+        <v>15000000</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1706,11 +1706,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Assane Diao</t>
+          <t>Maximilian Beier</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1719,29 +1719,29 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1252</v>
+        <v>1591</v>
       </c>
       <c r="H29" t="n">
-        <v>77.51936316695354</v>
+        <v>77.58182013769363</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>30000000</v>
+        <v>40000000</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>transfermarkt</t>
+          <t>heuristic</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
         <v>1965</v>
       </c>
       <c r="H30" t="n">
-        <v>76.74821428571428</v>
+        <v>77.17678571428571</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
@@ -1796,42 +1796,42 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nathaniel Brown</t>
+          <t>Bilal El Khannouss</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Eint Frankfurt</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1947</v>
+        <v>2182</v>
       </c>
       <c r="H31" t="n">
-        <v>76.5703477443609</v>
+        <v>77.17307692307693</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>40000000</v>
+        <v>35000000</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>heuristic</t>
+          <t>transfermarkt</t>
         </is>
       </c>
     </row>
@@ -1841,11 +1841,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Yaser Asprilla</t>
+          <t>Badredine Bouanani</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1854,25 +1854,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1405</v>
+        <v>1099</v>
       </c>
       <c r="H32" t="n">
-        <v>76.54683734939761</v>
+        <v>77.09008175559381</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>14000000</v>
+        <v>10000000</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -1886,11 +1886,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lucas Bergvall</t>
+          <t>Lamine Camara</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1899,25 +1899,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1212</v>
+        <v>2054</v>
       </c>
       <c r="H33" t="n">
-        <v>76.53571428571428</v>
+        <v>76.8</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>35000000</v>
+        <v>40000000</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lamine Camara</t>
+          <t>Andrey Santos</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2054</v>
+        <v>2855</v>
       </c>
       <c r="H34" t="n">
-        <v>76.4357142857143</v>
+        <v>76.77857142857144</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
@@ -1976,11 +1976,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Badredine Bouanani</t>
+          <t>Yeremi Pino</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1989,29 +1989,27 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1099</v>
+        <v>1934</v>
       </c>
       <c r="H35" t="n">
-        <v>76.37622633390707</v>
+        <v>76.59160929432014</v>
       </c>
       <c r="I35" t="n">
         <v>1</v>
       </c>
-      <c r="J35" t="n">
-        <v>10000000</v>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>transfermarkt</t>
+          <t>heuristic</t>
         </is>
       </c>
     </row>
@@ -2021,11 +2019,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Francisco Conceição</t>
+          <t>Santiago Castro</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2034,7 +2032,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2043,20 +2041,20 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1340</v>
+        <v>2294</v>
       </c>
       <c r="H36" t="n">
-        <v>76.36428571428573</v>
+        <v>76.59126743193247</v>
       </c>
       <c r="I36" t="n">
         <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>30000000</v>
+        <v>32000000</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>transfermarkt</t>
+          <t>heuristic</t>
         </is>
       </c>
     </row>
@@ -2066,42 +2064,42 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mateus Fernandes</t>
+          <t>Nathaniel Brown</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Eint Frankfurt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2909</v>
+        <v>1947</v>
       </c>
       <c r="H37" t="n">
-        <v>76.35714285714286</v>
+        <v>76.5703477443609</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>50000000</v>
+        <v>40000000</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>transfermarkt</t>
+          <t>heuristic</t>
         </is>
       </c>
     </row>
@@ -2111,15 +2109,15 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mathys Tel</t>
+          <t>Lucas Bergvall</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2133,20 +2131,20 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>911</v>
+        <v>1212</v>
       </c>
       <c r="H38" t="n">
-        <v>76.3046256454389</v>
+        <v>76.49285714285715</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>22000000</v>
+        <v>35000000</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>heuristic</t>
+          <t>transfermarkt</t>
         </is>
       </c>
     </row>
@@ -2156,11 +2154,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Yeremi Pino</t>
+          <t>Yaser Asprilla</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2169,7 +2167,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2178,18 +2176,20 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1934</v>
+        <v>1405</v>
       </c>
       <c r="H39" t="n">
-        <v>76.29341652323581</v>
+        <v>76.44743975903614</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
       </c>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>14000000</v>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>heuristic</t>
+          <t>transfermarkt</t>
         </is>
       </c>
     </row>
@@ -2199,38 +2199,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Andrey Santos</t>
+          <t>Jude Bellingham</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>2855</v>
+        <v>2488</v>
       </c>
       <c r="H40" t="n">
-        <v>76.07142857142858</v>
+        <v>76.40961538461539</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>40000000</v>
+        <v>130000000</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2244,11 +2244,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Maximilian Beier</t>
+          <t>Assane Diao</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2257,29 +2257,29 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1591</v>
+        <v>1252</v>
       </c>
       <c r="H41" t="n">
-        <v>75.83784423407917</v>
+        <v>76.3988812392427</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>40000000</v>
+        <v>30000000</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>heuristic</t>
+          <t>transfermarkt</t>
         </is>
       </c>
     </row>
@@ -2289,20 +2289,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mamadou Diakhon</t>
+          <t>Hákon Arnar Haraldsson</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2311,16 +2311,16 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>858</v>
+        <v>1755</v>
       </c>
       <c r="H42" t="n">
-        <v>75.83666092943201</v>
+        <v>76.39711538461539</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>7000000</v>
+        <v>25000000</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2334,11 +2334,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lucas Stassin</t>
+          <t>Francisco Conceição</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2347,29 +2347,29 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1887</v>
+        <v>1340</v>
       </c>
       <c r="H43" t="n">
-        <v>75.7493127176874</v>
+        <v>76.39139414802065</v>
       </c>
       <c r="I43" t="n">
         <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>15000000</v>
+        <v>30000000</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>heuristic</t>
+          <t>transfermarkt</t>
         </is>
       </c>
     </row>
@@ -2379,38 +2379,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bilal El Khannouss</t>
+          <t>Jonathan Rowe</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2182</v>
+        <v>807</v>
       </c>
       <c r="H44" t="n">
-        <v>75.73076923076924</v>
+        <v>76.39025387263339</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>35000000</v>
+        <v>28000000</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Gavi</t>
+          <t>Matias Fernandez-Pardo</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -2432,34 +2432,34 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1085</v>
+        <v>1065</v>
       </c>
       <c r="H45" t="n">
-        <v>75.69107142857143</v>
+        <v>76.08564974182444</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>30000000</v>
+        <v>35000000</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>transfermarkt</t>
+          <t>heuristic</t>
         </is>
       </c>
     </row>
@@ -2469,11 +2469,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pablo Barrios</t>
+          <t>Gavi</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2491,16 +2491,16 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2330</v>
+        <v>1085</v>
       </c>
       <c r="H46" t="n">
-        <v>75.65714285714286</v>
+        <v>75.84107142857144</v>
       </c>
       <c r="I46" t="n">
         <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>55000000</v>
+        <v>30000000</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2514,38 +2514,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Dario Essugo</t>
+          <t>Mateus Fernandes</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1938</v>
+        <v>2909</v>
       </c>
       <c r="H47" t="n">
-        <v>75.53227384405898</v>
+        <v>75.8</v>
       </c>
       <c r="I47" t="n">
         <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>15000000</v>
+        <v>50000000</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Jude Bellingham</t>
+          <t>Fermin López</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2581,16 +2581,16 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2488</v>
+        <v>1252</v>
       </c>
       <c r="H48" t="n">
-        <v>75.48653846153847</v>
+        <v>75.74862637362639</v>
       </c>
       <c r="I48" t="n">
         <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>130000000</v>
+        <v>100000000</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2604,11 +2604,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Diego Moreira</t>
+          <t>Ange-Yoan Bonny</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2617,29 +2617,29 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2568</v>
+        <v>2529</v>
       </c>
       <c r="H49" t="n">
-        <v>75.46506024096387</v>
+        <v>75.74323237833224</v>
       </c>
       <c r="I49" t="n">
         <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>25000000</v>
+        <v>35000000</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>transfermarkt</t>
+          <t>heuristic</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Elliot Anderson</t>
+          <t>Pape Matar Sarr</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Nott'ham Forest</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2728</v>
+        <v>1913</v>
       </c>
       <c r="H50" t="n">
-        <v>75.44285714285715</v>
+        <v>75.59821428571429</v>
       </c>
       <c r="I50" t="n">
         <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>75000000</v>
+        <v>30000000</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2694,42 +2694,42 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Santiago Castro</t>
+          <t>Pablo Barrios</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>2294</v>
+        <v>2330</v>
       </c>
       <c r="H51" t="n">
-        <v>75.40753249217343</v>
+        <v>75.59285714285714</v>
       </c>
       <c r="I51" t="n">
         <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>32000000</v>
+        <v>55000000</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>heuristic</t>
+          <t>transfermarkt</t>
         </is>
       </c>
     </row>
@@ -2739,38 +2739,38 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Hákon Arnar Haraldsson</t>
+          <t>Dario Essugo</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1755</v>
+        <v>1938</v>
       </c>
       <c r="H52" t="n">
-        <v>75.35865384615386</v>
+        <v>75.53227384405898</v>
       </c>
       <c r="I52" t="n">
         <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>25000000</v>
+        <v>15000000</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Eduardo Camavinga</t>
+          <t>Elliot Anderson</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -2797,25 +2797,25 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Nott'ham Forest</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1102</v>
+        <v>2728</v>
       </c>
       <c r="H53" t="n">
-        <v>75.28214285714287</v>
+        <v>75.52857142857144</v>
       </c>
       <c r="I53" t="n">
         <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>50000000</v>
+        <v>75000000</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -2829,11 +2829,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Matias Fernandez-Pardo</t>
+          <t>Williot Swedberg</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2842,29 +2842,29 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1065</v>
+        <v>1348</v>
       </c>
       <c r="H54" t="n">
-        <v>75.26336058519793</v>
+        <v>75.46437177280552</v>
       </c>
       <c r="I54" t="n">
         <v>1</v>
       </c>
       <c r="J54" t="n">
-        <v>35000000</v>
+        <v>20000000</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>heuristic</t>
+          <t>transfermarkt</t>
         </is>
       </c>
     </row>
@@ -2874,37 +2874,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Yehor Yarmoliuk</t>
+          <t>Mika Biereth</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1450</v>
+        <v>1228</v>
       </c>
       <c r="H55" t="n">
-        <v>75.06015037593986</v>
+        <v>75.44876714394134</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
       </c>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="n">
+        <v>15000000</v>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>heuristic</t>
@@ -2917,7 +2919,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Antonio Nusa</t>
+          <t>Facundo Buonanotte</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -2925,30 +2927,30 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1558</v>
+        <v>1523</v>
       </c>
       <c r="H56" t="n">
-        <v>74.96828743545611</v>
+        <v>75.24271978021979</v>
       </c>
       <c r="I56" t="n">
         <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>32000000</v>
+        <v>12000000</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -2962,7 +2964,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Pape Matar Sarr</t>
+          <t>Thierno Barry</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -2970,24 +2972,24 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1913</v>
+        <v>2323</v>
       </c>
       <c r="H57" t="n">
-        <v>74.82678571428572</v>
+        <v>75.20830329190778</v>
       </c>
       <c r="I57" t="n">
         <v>1</v>
@@ -2997,7 +2999,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>transfermarkt</t>
+          <t>heuristic</t>
         </is>
       </c>
     </row>
@@ -3007,11 +3009,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jonathan Rowe</t>
+          <t>Mathys Tel</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3020,29 +3022,29 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>807</v>
+        <v>911</v>
       </c>
       <c r="H58" t="n">
-        <v>74.71856712564544</v>
+        <v>75.20221600688468</v>
       </c>
       <c r="I58" t="n">
         <v>1</v>
       </c>
       <c r="J58" t="n">
-        <v>28000000</v>
+        <v>22000000</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>transfermarkt</t>
+          <t>heuristic</t>
         </is>
       </c>
     </row>
@@ -3052,38 +3054,38 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tyler Dibling</t>
+          <t>Eduardo Camavinga</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1874</v>
+        <v>1102</v>
       </c>
       <c r="H59" t="n">
-        <v>74.63373493975904</v>
+        <v>75.08928571428572</v>
       </c>
       <c r="I59" t="n">
         <v>1</v>
       </c>
       <c r="J59" t="n">
-        <v>17000000</v>
+        <v>50000000</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -3097,11 +3099,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Amadou Koné</t>
+          <t>Yehor Yarmoliuk</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3110,29 +3112,27 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1293</v>
+        <v>1450</v>
       </c>
       <c r="H60" t="n">
-        <v>74.6016447368421</v>
+        <v>75.06015037593986</v>
       </c>
       <c r="I60" t="n">
         <v>1</v>
       </c>
-      <c r="J60" t="n">
-        <v>7000000</v>
-      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>transfermarkt</t>
+          <t>heuristic</t>
         </is>
       </c>
     </row>
@@ -3142,42 +3142,42 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ethan Nwaneri</t>
+          <t>Lucas Stassin</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>895</v>
+        <v>1887</v>
       </c>
       <c r="H61" t="n">
-        <v>74.42651098901099</v>
+        <v>74.88184283816933</v>
       </c>
       <c r="I61" t="n">
         <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>35000000</v>
+        <v>15000000</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>transfermarkt</t>
+          <t>heuristic</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
         <v>2225</v>
       </c>
       <c r="H62" t="n">
-        <v>74.38571428571429</v>
+        <v>74.87857142857143</v>
       </c>
       <c r="I62" t="n">
         <v>1</v>
@@ -3232,38 +3232,38 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ernest Nuamah</t>
+          <t>Ethan Nwaneri</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1052</v>
+        <v>895</v>
       </c>
       <c r="H63" t="n">
-        <v>74.35636833046472</v>
+        <v>74.83035714285714</v>
       </c>
       <c r="I63" t="n">
         <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>10000000</v>
+        <v>35000000</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ange-Yoan Bonny</t>
+          <t>Ernest Nuamah</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -3290,29 +3290,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>2529</v>
+        <v>1052</v>
       </c>
       <c r="H64" t="n">
-        <v>74.34262996869367</v>
+        <v>74.81721170395869</v>
       </c>
       <c r="I64" t="n">
         <v>1</v>
       </c>
       <c r="J64" t="n">
-        <v>35000000</v>
+        <v>10000000</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>heuristic</t>
+          <t>transfermarkt</t>
         </is>
       </c>
     </row>
@@ -3322,38 +3322,38 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Hugo Álvarez</t>
+          <t>Hugo Larsson</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Eint Frankfurt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1572</v>
+        <v>2393</v>
       </c>
       <c r="H65" t="n">
-        <v>74.31798623063683</v>
+        <v>74.71428571428571</v>
       </c>
       <c r="I65" t="n">
         <v>1</v>
       </c>
       <c r="J65" t="n">
-        <v>8000000</v>
+        <v>28000000</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -3367,11 +3367,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Giuliano Simeone</t>
+          <t>Antonio Nusa</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -3380,25 +3380,25 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1926</v>
+        <v>1558</v>
       </c>
       <c r="H66" t="n">
-        <v>74.30778829604131</v>
+        <v>74.6158777969019</v>
       </c>
       <c r="I66" t="n">
         <v>1</v>
       </c>
       <c r="J66" t="n">
-        <v>40000000</v>
+        <v>32000000</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -3412,38 +3412,38 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Hugo Larsson</t>
+          <t>Amadou Koné</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Eint Frankfurt</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>2393</v>
+        <v>1293</v>
       </c>
       <c r="H67" t="n">
-        <v>74.24285714285715</v>
+        <v>74.6016447368421</v>
       </c>
       <c r="I67" t="n">
         <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>28000000</v>
+        <v>7000000</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Valentin Atangana Edoa</t>
+          <t>Tyler Dibling</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -3465,32 +3465,34 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>2854</v>
+        <v>1874</v>
       </c>
       <c r="H68" t="n">
-        <v>74.09967105263158</v>
+        <v>74.48012048192771</v>
       </c>
       <c r="I68" t="n">
         <v>1</v>
       </c>
-      <c r="J68" t="inlineStr"/>
+      <c r="J68" t="n">
+        <v>17000000</v>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>heuristic</t>
+          <t>transfermarkt</t>
         </is>
       </c>
     </row>
@@ -3500,42 +3502,42 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kévin Danois</t>
+          <t>Liam Delap</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1460</v>
+        <v>2593</v>
       </c>
       <c r="H69" t="n">
-        <v>73.99285714285715</v>
+        <v>74.33635862347026</v>
       </c>
       <c r="I69" t="n">
         <v>1</v>
       </c>
       <c r="J69" t="n">
-        <v>20000000</v>
+        <v>28000000</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>transfermarkt</t>
+          <t>heuristic</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3547,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Williot Swedberg</t>
+          <t>Habib Diarra</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -3553,30 +3555,30 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1348</v>
+        <v>2352</v>
       </c>
       <c r="H70" t="n">
-        <v>73.99148020654044</v>
+        <v>74.28447694038246</v>
       </c>
       <c r="I70" t="n">
         <v>1</v>
       </c>
       <c r="J70" t="n">
-        <v>20000000</v>
+        <v>35000000</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -3590,38 +3592,38 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Facundo Buonanotte</t>
+          <t>Hugo Álvarez</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>1523</v>
+        <v>1572</v>
       </c>
       <c r="H71" t="n">
-        <v>73.8581043956044</v>
+        <v>74.27280550774528</v>
       </c>
       <c r="I71" t="n">
         <v>1</v>
       </c>
       <c r="J71" t="n">
-        <v>12000000</v>
+        <v>8000000</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -3635,7 +3637,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Soungoutou Magassa</t>
+          <t>Kévin Danois</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -3643,12 +3645,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3657,16 +3659,16 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1025</v>
+        <v>1460</v>
       </c>
       <c r="H72" t="n">
-        <v>73.82852887632467</v>
+        <v>74.25</v>
       </c>
       <c r="I72" t="n">
         <v>1</v>
       </c>
       <c r="J72" t="n">
-        <v>17000000</v>
+        <v>20000000</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -3680,42 +3682,42 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Lesley Ugochukwu</t>
+          <t>Matthis Abline</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1655</v>
+        <v>2768</v>
       </c>
       <c r="H73" t="n">
-        <v>73.77514097744361</v>
+        <v>74.24252502134522</v>
       </c>
       <c r="I73" t="n">
         <v>1</v>
       </c>
       <c r="J73" t="n">
-        <v>22000000</v>
+        <v>20000000</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>transfermarkt</t>
+          <t>heuristic</t>
         </is>
       </c>
     </row>
@@ -3725,20 +3727,20 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Habib Diarra</t>
+          <t>Valentin Atangana Edoa</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3747,20 +3749,18 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>2352</v>
+        <v>2854</v>
       </c>
       <c r="H74" t="n">
-        <v>73.68447694038245</v>
+        <v>74.09967105263158</v>
       </c>
       <c r="I74" t="n">
         <v>1</v>
       </c>
-      <c r="J74" t="n">
-        <v>35000000</v>
-      </c>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>transfermarkt</t>
+          <t>heuristic</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fermin López</t>
+          <t>Giuliano Simeone</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3792,16 +3792,16 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1252</v>
+        <v>1926</v>
       </c>
       <c r="H75" t="n">
-        <v>73.67170329670331</v>
+        <v>74.06381239242685</v>
       </c>
       <c r="I75" t="n">
         <v>1</v>
       </c>
       <c r="J75" t="n">
-        <v>100000000</v>
+        <v>40000000</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -3815,42 +3815,42 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Thierno Barry</t>
+          <t>Senny Mayulu</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Paris S-G</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>2323</v>
+        <v>808</v>
       </c>
       <c r="H76" t="n">
-        <v>73.39203823166683</v>
+        <v>74</v>
       </c>
       <c r="I76" t="n">
         <v>1</v>
       </c>
       <c r="J76" t="n">
-        <v>30000000</v>
+        <v>40000000</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>heuristic</t>
+          <t>transfermarkt</t>
         </is>
       </c>
     </row>
@@ -3860,15 +3860,15 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Mika Biereth</t>
+          <t>Soungoutou Magassa</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3882,20 +3882,20 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>1228</v>
+        <v>1025</v>
       </c>
       <c r="H77" t="n">
-        <v>73.3072008788811</v>
+        <v>73.82852887632467</v>
       </c>
       <c r="I77" t="n">
         <v>1</v>
       </c>
       <c r="J77" t="n">
-        <v>15000000</v>
+        <v>17000000</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>heuristic</t>
+          <t>transfermarkt</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Benjamín Domínguez</t>
+          <t>Lesley Ugochukwu</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -3913,32 +3913,34 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>1281</v>
+        <v>1655</v>
       </c>
       <c r="H78" t="n">
-        <v>73.27110585197934</v>
+        <v>73.77514097744361</v>
       </c>
       <c r="I78" t="n">
         <v>1</v>
       </c>
-      <c r="J78" t="inlineStr"/>
+      <c r="J78" t="n">
+        <v>22000000</v>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>heuristic</t>
+          <t>transfermarkt</t>
         </is>
       </c>
     </row>
@@ -3948,38 +3950,38 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ngal'Ayel Mukau</t>
+          <t>Brajan Gruda</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>1190</v>
+        <v>687</v>
       </c>
       <c r="H79" t="n">
-        <v>73.26038533834587</v>
+        <v>73.71607142857144</v>
       </c>
       <c r="I79" t="n">
         <v>1</v>
       </c>
       <c r="J79" t="n">
-        <v>15000000</v>
+        <v>28000000</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -3993,42 +3995,42 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Matthis Abline</t>
+          <t>Omari Hutchinson</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>2768</v>
+        <v>2583</v>
       </c>
       <c r="H80" t="n">
-        <v>73.25758526230908</v>
+        <v>73.56730769230769</v>
       </c>
       <c r="I80" t="n">
         <v>1</v>
       </c>
       <c r="J80" t="n">
-        <v>20000000</v>
+        <v>30000000</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>heuristic</t>
+          <t>transfermarkt</t>
         </is>
       </c>
     </row>
@@ -4038,38 +4040,38 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Omari Hutchinson</t>
+          <t>Mamadou Diakhon</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>2583</v>
+        <v>858</v>
       </c>
       <c r="H81" t="n">
-        <v>73.10576923076923</v>
+        <v>73.48726333907057</v>
       </c>
       <c r="I81" t="n">
         <v>1</v>
       </c>
       <c r="J81" t="n">
-        <v>30000000</v>
+        <v>7000000</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -4083,42 +4085,40 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Senny Mayulu</t>
+          <t>Benjamín Domínguez</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Paris S-G</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>808</v>
+        <v>1281</v>
       </c>
       <c r="H82" t="n">
-        <v>73.01428571428572</v>
+        <v>73.31628657487092</v>
       </c>
       <c r="I82" t="n">
         <v>1</v>
       </c>
-      <c r="J82" t="n">
-        <v>40000000</v>
-      </c>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>transfermarkt</t>
+          <t>heuristic</t>
         </is>
       </c>
     </row>
@@ -4128,42 +4128,42 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Liam Delap</t>
+          <t>Ngal'Ayel Mukau</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>2593</v>
+        <v>1190</v>
       </c>
       <c r="H83" t="n">
-        <v>73.00804537045821</v>
+        <v>73.26038533834587</v>
       </c>
       <c r="I83" t="n">
         <v>1</v>
       </c>
       <c r="J83" t="n">
-        <v>28000000</v>
+        <v>15000000</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>heuristic</t>
+          <t>transfermarkt</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Arthur Vermeeren</t>
+          <t>Jean Mattéo Bahoya</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Eint Frankfurt</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4195,16 +4195,16 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>1572</v>
+        <v>921</v>
       </c>
       <c r="H84" t="n">
-        <v>73.00672325498786</v>
+        <v>73.24554647160069</v>
       </c>
       <c r="I84" t="n">
         <v>1</v>
       </c>
       <c r="J84" t="n">
-        <v>20000000</v>
+        <v>25000000</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -4218,11 +4218,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Adam Wharton</t>
+          <t>Arthur Vermeeren</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -4231,25 +4231,25 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>1318</v>
+        <v>1572</v>
       </c>
       <c r="H85" t="n">
-        <v>72.8579417293233</v>
+        <v>73.00672325498786</v>
       </c>
       <c r="I85" t="n">
         <v>1</v>
       </c>
       <c r="J85" t="n">
-        <v>70000000</v>
+        <v>20000000</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -4263,38 +4263,38 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Jean Mattéo Bahoya</t>
+          <t>Adam Wharton</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Eint Frankfurt</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>921</v>
+        <v>1318</v>
       </c>
       <c r="H86" t="n">
-        <v>72.85699225473323</v>
+        <v>72.8579417293233</v>
       </c>
       <c r="I86" t="n">
         <v>1</v>
       </c>
       <c r="J86" t="n">
-        <v>25000000</v>
+        <v>70000000</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -4308,40 +4308,42 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Emanuel Emegha</t>
+          <t>Stefan Bajcetic</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2293</v>
+        <v>969</v>
       </c>
       <c r="H87" t="n">
-        <v>72.82230813015843</v>
+        <v>72.8093515037594</v>
       </c>
       <c r="I87" t="n">
         <v>1</v>
       </c>
-      <c r="J87" t="inlineStr"/>
+      <c r="J87" t="n">
+        <v>4000000</v>
+      </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>heuristic</t>
+          <t>transfermarkt</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4353,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Stefan Bajcetic</t>
+          <t>Diego Moreira</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -4359,30 +4361,30 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>969</v>
+        <v>2568</v>
       </c>
       <c r="H88" t="n">
-        <v>72.8093515037594</v>
+        <v>72.77228915662651</v>
       </c>
       <c r="I88" t="n">
         <v>1</v>
       </c>
       <c r="J88" t="n">
-        <v>4000000</v>
+        <v>25000000</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -4396,38 +4398,38 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Kobbie Mainoo</t>
+          <t>Mario Martín</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Manchester Utd</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>1651</v>
+        <v>1748</v>
       </c>
       <c r="H89" t="n">
-        <v>72.78749999999999</v>
+        <v>72.69953895565686</v>
       </c>
       <c r="I89" t="n">
         <v>1</v>
       </c>
       <c r="J89" t="n">
-        <v>70000000</v>
+        <v>10000000</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -4441,20 +4443,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Mario Martín</t>
+          <t>Jesus Rodríguez</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4463,20 +4465,20 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>1748</v>
+        <v>1111</v>
       </c>
       <c r="H90" t="n">
-        <v>72.69953895565686</v>
+        <v>72.66611445783133</v>
       </c>
       <c r="I90" t="n">
         <v>1</v>
       </c>
       <c r="J90" t="n">
-        <v>10000000</v>
+        <v>350000</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>transfermarkt</t>
+          <t>heuristic</t>
         </is>
       </c>
     </row>
@@ -4486,11 +4488,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Mikel Jauregizar</t>
+          <t>Kobbie Mainoo</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -4499,25 +4501,25 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Manchester Utd</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>2244</v>
+        <v>1651</v>
       </c>
       <c r="H91" t="n">
-        <v>72.69285714285715</v>
+        <v>72.6375</v>
       </c>
       <c r="I91" t="n">
         <v>1</v>
       </c>
       <c r="J91" t="n">
-        <v>30000000</v>
+        <v>70000000</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -4531,15 +4533,15 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Oscar Højlund</t>
+          <t>Fares Chaïbi</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4553,10 +4555,10 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>722</v>
+        <v>1013</v>
       </c>
       <c r="H92" t="n">
-        <v>72.55357142857143</v>
+        <v>72.60865384615386</v>
       </c>
       <c r="I92" t="n">
         <v>1</v>
@@ -4576,38 +4578,38 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Johann Lepenant</t>
+          <t>Mikel Jauregizar</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>2048</v>
+        <v>2244</v>
       </c>
       <c r="H93" t="n">
-        <v>72.40230263157895</v>
+        <v>72.58571428571429</v>
       </c>
       <c r="I93" t="n">
         <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>7000000</v>
+        <v>30000000</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -4621,7 +4623,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Benjamin Šeško</t>
+          <t>Emanuel Emegha</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -4634,26 +4636,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>2380</v>
+        <v>2293</v>
       </c>
       <c r="H94" t="n">
-        <v>72.27336946210038</v>
+        <v>72.49700692533915</v>
       </c>
       <c r="I94" t="n">
         <v>1</v>
       </c>
-      <c r="J94" t="n">
-        <v>75000000</v>
-      </c>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
           <t>heuristic</t>
@@ -4666,42 +4666,42 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Jesus Rodríguez</t>
+          <t>Johann Lepenant</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Winger</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>1111</v>
+        <v>2048</v>
       </c>
       <c r="H95" t="n">
-        <v>72.2414156626506</v>
+        <v>72.40230263157895</v>
       </c>
       <c r="I95" t="n">
         <v>1</v>
       </c>
       <c r="J95" t="n">
-        <v>350000</v>
+        <v>7000000</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>heuristic</t>
+          <t>transfermarkt</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Alessandro Bianco</t>
+          <t>Luka Sučić</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -4724,25 +4724,25 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>2600</v>
+        <v>1792</v>
       </c>
       <c r="H96" t="n">
-        <v>71.88571428571429</v>
+        <v>72.16428571428571</v>
       </c>
       <c r="I96" t="n">
         <v>1</v>
       </c>
       <c r="J96" t="n">
-        <v>4000000</v>
+        <v>10000000</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Brajan Gruda</t>
+          <t>Félix Lemaréchal</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -4769,25 +4769,25 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>687</v>
+        <v>1779</v>
       </c>
       <c r="H97" t="n">
-        <v>71.69684065934067</v>
+        <v>72.16030219780221</v>
       </c>
       <c r="I97" t="n">
         <v>1</v>
       </c>
       <c r="J97" t="n">
-        <v>28000000</v>
+        <v>6000000</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -4801,11 +4801,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Myles Lewis-Skelly</t>
+          <t>Oscar Højlund</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -4814,25 +4814,25 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Eint Frankfurt</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>1369</v>
+        <v>722</v>
       </c>
       <c r="H98" t="n">
-        <v>71.64111712598425</v>
+        <v>71.99642857142858</v>
       </c>
       <c r="I98" t="n">
         <v>1</v>
       </c>
       <c r="J98" t="n">
-        <v>45000000</v>
+        <v>15000000</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -4846,38 +4846,38 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Hugo Sotelo</t>
+          <t>Paul Nebel</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>1254</v>
+        <v>2345</v>
       </c>
       <c r="H99" t="n">
-        <v>71.63214285714287</v>
+        <v>71.80961538461538</v>
       </c>
       <c r="I99" t="n">
         <v>1</v>
       </c>
       <c r="J99" t="n">
-        <v>5000000</v>
+        <v>18000000</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -4891,11 +4891,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Archie Gray</t>
+          <t>Alessandro Bianco</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -4904,25 +4904,25 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>1751</v>
+        <v>2600</v>
       </c>
       <c r="H100" t="n">
-        <v>71.51560742407199</v>
+        <v>71.80000000000001</v>
       </c>
       <c r="I100" t="n">
         <v>1</v>
       </c>
       <c r="J100" t="n">
-        <v>35000000</v>
+        <v>4000000</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -4936,42 +4936,42 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Jordan James</t>
+          <t>Vitor Roque</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Winger</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1178</v>
+        <v>1235</v>
       </c>
       <c r="H101" t="n">
-        <v>71.45357142857142</v>
+        <v>71.63674148223943</v>
       </c>
       <c r="I101" t="n">
         <v>1</v>
       </c>
       <c r="J101" t="n">
-        <v>12000000</v>
+        <v>38000000</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>transfermarkt</t>
+          <t>heuristic</t>
         </is>
       </c>
     </row>
